--- a/slide_classification/TCGA_Results/Caption_based_aggregation/H-Optimus-1/1-MSIH/Output/cross_valid_avg_eval_metrics.xlsx
+++ b/slide_classification/TCGA_Results/Caption_based_aggregation/H-Optimus-1/1-MSIH/Output/cross_valid_avg_eval_metrics.xlsx
@@ -8,6 +8,7 @@
   </bookViews>
   <sheets>
     <sheet name="baseline" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Summary" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -578,26 +579,22 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>[[84  4]
- [ 5 10]]</t>
+          <t>[[84, 4], [5, 10]]</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>[[82  2]
- [ 6  7]]</t>
+          <t>[[82, 2], [6, 7]]</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>[[87  5]
- [ 6 14]]</t>
+          <t>[[87, 5], [6, 14]]</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>[[87  2]
- [ 5  7]]</t>
+          <t>[[87, 2], [5, 7]]</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -613,19 +610,19 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.8446601941747572</v>
+        <v>0.8932038834951457</v>
       </c>
       <c r="C8" t="n">
         <v>0.8865979381443299</v>
       </c>
       <c r="D8" t="n">
-        <v>0.8660714285714286</v>
+        <v>0.8303571428571429</v>
       </c>
       <c r="E8" t="n">
-        <v>0.8415841584158416</v>
+        <v>0.801980198019802</v>
       </c>
       <c r="F8" t="n">
-        <v>0.8597284298265893</v>
+        <v>0.8530347906291051</v>
       </c>
     </row>
     <row r="9">
@@ -635,19 +632,19 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.8537878787878788</v>
+        <v>0.8545454545454545</v>
       </c>
       <c r="C9" t="n">
         <v>0.771978021978022</v>
       </c>
       <c r="D9" t="n">
-        <v>0.8597826086956522</v>
+        <v>0.8184782608695653</v>
       </c>
       <c r="E9" t="n">
-        <v>0.8019662921348314</v>
+        <v>0.7434456928838951</v>
       </c>
       <c r="F9" t="n">
-        <v>0.8218787003990962</v>
+        <v>0.7971118575692342</v>
       </c>
     </row>
     <row r="10">
@@ -657,19 +654,19 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.7607433217189314</v>
+        <v>0.8106934001670844</v>
       </c>
       <c r="C10" t="n">
         <v>0.7633621645597694</v>
       </c>
       <c r="D10" t="n">
-        <v>0.8040816326530612</v>
+        <v>0.7588121953983906</v>
       </c>
       <c r="E10" t="n">
-        <v>0.7170868347338936</v>
+        <v>0.6619812583668006</v>
       </c>
       <c r="F10" t="n">
-        <v>0.7613184884164139</v>
+        <v>0.7487122546230112</v>
       </c>
     </row>
     <row r="11">
@@ -679,19 +676,19 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.8611684313791822</v>
+        <v>0.8992708307986795</v>
       </c>
       <c r="C11" t="n">
         <v>0.888358449195538</v>
       </c>
       <c r="D11" t="n">
-        <v>0.8749271137026239</v>
+        <v>0.8432586907595407</v>
       </c>
       <c r="E11" t="n">
-        <v>0.8601658485176249</v>
+        <v>0.8278261561095868</v>
       </c>
       <c r="F11" t="n">
-        <v>0.8711549606987422</v>
+        <v>0.8646785317158363</v>
       </c>
     </row>
     <row r="12">
@@ -701,19 +698,19 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.9303030303030304</v>
+        <v>0.9265151515151514</v>
       </c>
       <c r="C12" t="n">
-        <v>0.8836996336996337</v>
+        <v>0.8974358974358974</v>
       </c>
       <c r="D12" t="n">
-        <v>0.9293478260869564</v>
+        <v>0.9391304347826087</v>
       </c>
       <c r="E12" t="n">
         <v>0.8923220973782772</v>
       </c>
       <c r="F12" t="n">
-        <v>0.9089181468669744</v>
+        <v>0.9138508952779836</v>
       </c>
     </row>
     <row r="13">
@@ -724,31 +721,27 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>[[74 14]
- [ 2 13]]</t>
+          <t>[[80, 8], [3, 12]]</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>[[78  6]
- [ 5  8]]</t>
+          <t>[[78, 6], [5, 8]]</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>[[80 12]
- [ 3 17]]</t>
+          <t>[[77, 15], [4, 16]]</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>[[76 13]
- [ 3  9]]</t>
+          <t>[[73, 16], [4, 8]]</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>[[77, 11], [3, 12]]</t>
+          <t>[[77, 11], [4, 11]]</t>
         </is>
       </c>
     </row>
@@ -762,7 +755,7 @@
         <v>0.8446601941747572</v>
       </c>
       <c r="C14" t="n">
-        <v>0.8865979381443299</v>
+        <v>0.8762886597938144</v>
       </c>
       <c r="D14" t="n">
         <v>0.8482142857142857</v>
@@ -771,7 +764,7 @@
         <v>0.8613861386138614</v>
       </c>
       <c r="F14" t="n">
-        <v>0.8602146391618085</v>
+        <v>0.8576373195741797</v>
       </c>
     </row>
     <row r="15">
@@ -784,7 +777,7 @@
         <v>0.6325757575757576</v>
       </c>
       <c r="C15" t="n">
-        <v>0.5769230769230769</v>
+        <v>0.5384615384615384</v>
       </c>
       <c r="D15" t="n">
         <v>0.633695652173913</v>
@@ -793,7 +786,7 @@
         <v>0.5969101123595506</v>
       </c>
       <c r="F15" t="n">
-        <v>0.6100261497580746</v>
+        <v>0.60041076514269</v>
       </c>
     </row>
     <row r="16">
@@ -806,7 +799,7 @@
         <v>0.6478632478632479</v>
       </c>
       <c r="C16" t="n">
-        <v>0.6026070763500931</v>
+        <v>0.5380952380952381</v>
       </c>
       <c r="D16" t="n">
         <v>0.6633068081343944</v>
@@ -815,7 +808,7 @@
         <v>0.6115384615384616</v>
       </c>
       <c r="F16" t="n">
-        <v>0.6313288984715493</v>
+        <v>0.6152009389078354</v>
       </c>
     </row>
     <row r="17">
@@ -828,7 +821,7 @@
         <v>0.834436976184549</v>
       </c>
       <c r="C17" t="n">
-        <v>0.8485016030255909</v>
+        <v>0.8273932253313697</v>
       </c>
       <c r="D17" t="n">
         <v>0.8237084754326134</v>
@@ -837,7 +830,7 @@
         <v>0.8490479817212491</v>
       </c>
       <c r="F17" t="n">
-        <v>0.8389237590910006</v>
+        <v>0.8336466646674452</v>
       </c>
     </row>
     <row r="18">
@@ -850,7 +843,7 @@
         <v>0.7606060606060606</v>
       </c>
       <c r="C18" t="n">
-        <v>0.7486263736263735</v>
+        <v>0.7857142857142858</v>
       </c>
       <c r="D18" t="n">
         <v>0.7467391304347826</v>
@@ -859,7 +852,7 @@
         <v>0.8132022471910113</v>
       </c>
       <c r="F18" t="n">
-        <v>0.767293452964557</v>
+        <v>0.7765654309865351</v>
       </c>
     </row>
     <row r="19">
@@ -870,26 +863,22 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>[[82  6]
- [10  5]]</t>
+          <t>[[82, 6], [10, 5]]</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>[[84  0]
- [11  2]]</t>
+          <t>[[84, 0], [12, 1]]</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>[[89  3]
- [14  6]]</t>
+          <t>[[89, 3], [14, 6]]</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>[[84  5]
- [ 9  3]]</t>
+          <t>[[84, 5], [9, 3]]</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1016,26 +1005,22 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>[[74 14]
- [ 4 11]]</t>
+          <t>[[74, 14], [4, 11]]</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>[[69 15]
- [ 7  6]]</t>
+          <t>[[69, 15], [7, 6]]</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>[[80 12]
- [ 6 14]]</t>
+          <t>[[80, 12], [6, 14]]</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>[[77 12]
- [ 3  9]]</t>
+          <t>[[77, 12], [3, 9]]</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1051,19 +1036,19 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>0.9029126213592233</v>
+        <v>0.912621359223301</v>
       </c>
       <c r="C26" t="n">
-        <v>0.9072164948453608</v>
+        <v>0.9175257731958762</v>
       </c>
       <c r="D26" t="n">
         <v>0.8660714285714286</v>
       </c>
       <c r="E26" t="n">
-        <v>0.9108910891089109</v>
+        <v>0.8910891089108911</v>
       </c>
       <c r="F26" t="n">
-        <v>0.8967729084712308</v>
+        <v>0.8968269174753742</v>
       </c>
     </row>
     <row r="27">
@@ -1073,19 +1058,19 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>0.6943181818181818</v>
+        <v>0.7276515151515152</v>
       </c>
       <c r="C27" t="n">
-        <v>0.6863553113553114</v>
+        <v>0.6923076923076923</v>
       </c>
       <c r="D27" t="n">
-        <v>0.6641304347826087</v>
+        <v>0.683695652173913</v>
       </c>
       <c r="E27" t="n">
-        <v>0.6970973782771536</v>
+        <v>0.649812734082397</v>
       </c>
       <c r="F27" t="n">
-        <v>0.6854753265583139</v>
+        <v>0.6883668984288794</v>
       </c>
     </row>
     <row r="28">
@@ -1095,19 +1080,19 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>0.7455533596837944</v>
+        <v>0.7797576621525303</v>
       </c>
       <c r="C28" t="n">
-        <v>0.7374436090225565</v>
+        <v>0.7550505050505051</v>
       </c>
       <c r="D28" t="n">
-        <v>0.7029177718832892</v>
+        <v>0.7192044125020892</v>
       </c>
       <c r="E28" t="n">
-        <v>0.7385677308024159</v>
+        <v>0.6804716709807306</v>
       </c>
       <c r="F28" t="n">
-        <v>0.7311206178480141</v>
+        <v>0.7336210626714639</v>
       </c>
     </row>
     <row r="29">
@@ -1117,19 +1102,19 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>0.8873709658851069</v>
+        <v>0.9009957857296086</v>
       </c>
       <c r="C29" t="n">
-        <v>0.8919804666304938</v>
+        <v>0.9010725814849527</v>
       </c>
       <c r="D29" t="n">
-        <v>0.8444486547934825</v>
+        <v>0.8497528712303908</v>
       </c>
       <c r="E29" t="n">
-        <v>0.9003835672609538</v>
+        <v>0.8782465822078326</v>
       </c>
       <c r="F29" t="n">
-        <v>0.8810459136425093</v>
+        <v>0.8825169551631961</v>
       </c>
     </row>
     <row r="30">
@@ -1139,19 +1124,19 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>0.971969696969697</v>
+        <v>0.95</v>
       </c>
       <c r="C30" t="n">
-        <v>0.8388278388278388</v>
+        <v>0.8374542124542125</v>
       </c>
       <c r="D30" t="n">
-        <v>0.9309782608695651</v>
+        <v>0.9249999999999999</v>
       </c>
       <c r="E30" t="n">
-        <v>0.9054307116104869</v>
+        <v>0.9044943820224719</v>
       </c>
       <c r="F30" t="n">
-        <v>0.9118016270693969</v>
+        <v>0.904237148619171</v>
       </c>
     </row>
     <row r="31">
@@ -1162,31 +1147,413 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>[[87  1]
- [ 9  6]]</t>
+          <t>[[87, 1], [8, 7]]</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>[[83  1]
- [ 8  5]]</t>
+          <t>[[84, 0], [8, 5]]</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>[[90  2]
- [13  7]]</t>
+          <t>[[89, 3], [12, 8]]</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>[[87  2]
- [ 7  5]]</t>
+          <t>[[86, 3], [8, 4]]</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>[[87, 2], [9, 6]]</t>
+          <t>[[86, 2], [9, 6]]</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:P6"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Method</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Model</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Classifier</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>N_folds</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>N_test</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>acc</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>acc_sd</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>bacc</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>bacc_sd</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>macro_f1</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>macro_f1_sd</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>weighted_f1</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>weighted_f1_sd</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>auroc</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>auroc_sd</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>conf_matrix</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Caption_based_aggregation</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>H-Optimus-1</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>lin</t>
+        </is>
+      </c>
+      <c r="D2" t="n">
+        <v>4</v>
+      </c>
+      <c r="E2" t="n">
+        <v>413</v>
+      </c>
+      <c r="F2" t="n">
+        <v>0.9156564790029555</v>
+      </c>
+      <c r="G2" t="n">
+        <v>0.01038271851042879</v>
+      </c>
+      <c r="H2" t="n">
+        <v>0.7927972166247691</v>
+      </c>
+      <c r="I2" t="n">
+        <v>0.0256418852306925</v>
+      </c>
+      <c r="J2" t="n">
+        <v>0.814392701906261</v>
+      </c>
+      <c r="K2" t="n">
+        <v>0.01249800848784484</v>
+      </c>
+      <c r="L2" t="n">
+        <v>0.9123644309954853</v>
+      </c>
+      <c r="M2" t="n">
+        <v>0.009103518695269618</v>
+      </c>
+      <c r="N2" t="n">
+        <v>0.9249574893840894</v>
+      </c>
+      <c r="O2" t="n">
+        <v>0.01726913439468407</v>
+      </c>
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>[[85, 3], [6, 10]]</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Caption_based_aggregation</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>H-Optimus-1</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>ann</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
+        <v>4</v>
+      </c>
+      <c r="E3" t="n">
+        <v>413</v>
+      </c>
+      <c r="F3" t="n">
+        <v>0.8530347906291051</v>
+      </c>
+      <c r="G3" t="n">
+        <v>0.03827821844006202</v>
+      </c>
+      <c r="H3" t="n">
+        <v>0.7971118575692342</v>
+      </c>
+      <c r="I3" t="n">
+        <v>0.04262308111569167</v>
+      </c>
+      <c r="J3" t="n">
+        <v>0.7487122546230112</v>
+      </c>
+      <c r="K3" t="n">
+        <v>0.05403831228714425</v>
+      </c>
+      <c r="L3" t="n">
+        <v>0.8646785317158363</v>
+      </c>
+      <c r="M3" t="n">
+        <v>0.02989261121957837</v>
+      </c>
+      <c r="N3" t="n">
+        <v>0.9138508952779836</v>
+      </c>
+      <c r="O3" t="n">
+        <v>0.01957281147899201</v>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>[[77, 11], [4, 11]]</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Caption_based_aggregation</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>H-Optimus-1</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>knn</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>4</v>
+      </c>
+      <c r="E4" t="n">
+        <v>413</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0.8576373195741797</v>
+      </c>
+      <c r="G4" t="n">
+        <v>0.01244111617719536</v>
+      </c>
+      <c r="H4" t="n">
+        <v>0.60041076514269</v>
+      </c>
+      <c r="I4" t="n">
+        <v>0.03870539916859589</v>
+      </c>
+      <c r="J4" t="n">
+        <v>0.6152009389078354</v>
+      </c>
+      <c r="K4" t="n">
+        <v>0.04832107179746885</v>
+      </c>
+      <c r="L4" t="n">
+        <v>0.8336466646674452</v>
+      </c>
+      <c r="M4" t="n">
+        <v>0.009691468775205851</v>
+      </c>
+      <c r="N4" t="n">
+        <v>0.7765654309865351</v>
+      </c>
+      <c r="O4" t="n">
+        <v>0.02534890309251416</v>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>[[85, 4], [11, 4]]</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Caption_based_aggregation</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>H-Optimus-1</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>proto</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>4</v>
+      </c>
+      <c r="E5" t="n">
+        <v>413</v>
+      </c>
+      <c r="F5" t="n">
+        <v>0.8223023643839569</v>
+      </c>
+      <c r="G5" t="n">
+        <v>0.02983354621304339</v>
+      </c>
+      <c r="H5" t="n">
+        <v>0.7552429017408255</v>
+      </c>
+      <c r="I5" t="n">
+        <v>0.06627525460109976</v>
+      </c>
+      <c r="J5" t="n">
+        <v>0.7026595809004957</v>
+      </c>
+      <c r="K5" t="n">
+        <v>0.05615984657969733</v>
+      </c>
+      <c r="L5" t="n">
+        <v>0.8377183164099875</v>
+      </c>
+      <c r="M5" t="n">
+        <v>0.02693069144947014</v>
+      </c>
+      <c r="N5" t="n">
+        <v>0.8323406686132626</v>
+      </c>
+      <c r="O5" t="n">
+        <v>0.134284059266447</v>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>[[75, 13], [5, 10]]</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Caption_based_aggregation</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>H-Optimus-1</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>rf</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>4</v>
+      </c>
+      <c r="E6" t="n">
+        <v>413</v>
+      </c>
+      <c r="F6" t="n">
+        <v>0.8968269174753742</v>
+      </c>
+      <c r="G6" t="n">
+        <v>0.02035147146467664</v>
+      </c>
+      <c r="H6" t="n">
+        <v>0.6883668984288794</v>
+      </c>
+      <c r="I6" t="n">
+        <v>0.02769049971321298</v>
+      </c>
+      <c r="J6" t="n">
+        <v>0.7336210626714639</v>
+      </c>
+      <c r="K6" t="n">
+        <v>0.03748501184324911</v>
+      </c>
+      <c r="L6" t="n">
+        <v>0.8825169551631961</v>
+      </c>
+      <c r="M6" t="n">
+        <v>0.02108020237348695</v>
+      </c>
+      <c r="N6" t="n">
+        <v>0.904237148619171</v>
+      </c>
+      <c r="O6" t="n">
+        <v>0.04178923693908196</v>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>[[86, 2], [9, 6]]</t>
         </is>
       </c>
     </row>

--- a/slide_classification/TCGA_Results/Caption_based_aggregation/H-Optimus-1/1-MSIH/Output/cross_valid_avg_eval_metrics.xlsx
+++ b/slide_classification/TCGA_Results/Caption_based_aggregation/H-Optimus-1/1-MSIH/Output/cross_valid_avg_eval_metrics.xlsx
@@ -752,19 +752,19 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.8446601941747572</v>
+        <v>0.8543689320388349</v>
       </c>
       <c r="C14" t="n">
-        <v>0.8762886597938144</v>
+        <v>0.8865979381443299</v>
       </c>
       <c r="D14" t="n">
-        <v>0.8482142857142857</v>
+        <v>0.8392857142857143</v>
       </c>
       <c r="E14" t="n">
         <v>0.8613861386138614</v>
       </c>
       <c r="F14" t="n">
-        <v>0.8576373195741797</v>
+        <v>0.8604096807706851</v>
       </c>
     </row>
     <row r="15">
@@ -774,19 +774,19 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.6325757575757576</v>
+        <v>0.6382575757575758</v>
       </c>
       <c r="C15" t="n">
-        <v>0.5384615384615384</v>
+        <v>0.5769230769230769</v>
       </c>
       <c r="D15" t="n">
-        <v>0.633695652173913</v>
+        <v>0.5695652173913043</v>
       </c>
       <c r="E15" t="n">
         <v>0.5969101123595506</v>
       </c>
       <c r="F15" t="n">
-        <v>0.60041076514269</v>
+        <v>0.595413995607877</v>
       </c>
     </row>
     <row r="16">
@@ -796,19 +796,19 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.6478632478632479</v>
+        <v>0.6585635359116022</v>
       </c>
       <c r="C16" t="n">
-        <v>0.5380952380952381</v>
+        <v>0.6026070763500931</v>
       </c>
       <c r="D16" t="n">
-        <v>0.6633068081343944</v>
+        <v>0.5800000000000001</v>
       </c>
       <c r="E16" t="n">
         <v>0.6115384615384616</v>
       </c>
       <c r="F16" t="n">
-        <v>0.6152009389078354</v>
+        <v>0.6131772684500393</v>
       </c>
     </row>
     <row r="17">
@@ -818,19 +818,19 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>0.834436976184549</v>
+        <v>0.8418173040819611</v>
       </c>
       <c r="C17" t="n">
-        <v>0.8273932253313697</v>
+        <v>0.8485016030255909</v>
       </c>
       <c r="D17" t="n">
-        <v>0.8237084754326134</v>
+        <v>0.7921428571428571</v>
       </c>
       <c r="E17" t="n">
         <v>0.8490479817212491</v>
       </c>
       <c r="F17" t="n">
-        <v>0.8336466646674452</v>
+        <v>0.8328774364929146</v>
       </c>
     </row>
     <row r="18">
@@ -840,19 +840,19 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>0.7606060606060606</v>
+        <v>0.7329545454545454</v>
       </c>
       <c r="C18" t="n">
-        <v>0.7857142857142858</v>
+        <v>0.7756410256410257</v>
       </c>
       <c r="D18" t="n">
-        <v>0.7467391304347826</v>
+        <v>0.7513586956521738</v>
       </c>
       <c r="E18" t="n">
         <v>0.8132022471910113</v>
       </c>
       <c r="F18" t="n">
-        <v>0.7765654309865351</v>
+        <v>0.768289128484689</v>
       </c>
     </row>
     <row r="19">
@@ -863,17 +863,17 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>[[82, 6], [10, 5]]</t>
+          <t>[[83, 5], [10, 5]]</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>[[84, 0], [12, 1]]</t>
+          <t>[[84, 0], [11, 2]]</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>[[89, 3], [14, 6]]</t>
+          <t>[[91, 1], [17, 3]]</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -883,7 +883,7 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>[[85, 4], [11, 4]]</t>
+          <t>[[86, 3], [12, 3]]</t>
         </is>
       </c>
     </row>
@@ -1406,38 +1406,38 @@
         <v>413</v>
       </c>
       <c r="F4" t="n">
-        <v>0.8576373195741797</v>
+        <v>0.8604096807706851</v>
       </c>
       <c r="G4" t="n">
-        <v>0.01244111617719536</v>
+        <v>0.01709891004923471</v>
       </c>
       <c r="H4" t="n">
-        <v>0.60041076514269</v>
+        <v>0.595413995607877</v>
       </c>
       <c r="I4" t="n">
-        <v>0.03870539916859589</v>
+        <v>0.02668278534221905</v>
       </c>
       <c r="J4" t="n">
-        <v>0.6152009389078354</v>
+        <v>0.6131772684500393</v>
       </c>
       <c r="K4" t="n">
-        <v>0.04832107179746885</v>
+        <v>0.02861406588123091</v>
       </c>
       <c r="L4" t="n">
-        <v>0.8336466646674452</v>
+        <v>0.8328774364929146</v>
       </c>
       <c r="M4" t="n">
-        <v>0.009691468775205851</v>
+        <v>0.02368980951885337</v>
       </c>
       <c r="N4" t="n">
-        <v>0.7765654309865351</v>
+        <v>0.768289128484689</v>
       </c>
       <c r="O4" t="n">
-        <v>0.02534890309251416</v>
+        <v>0.03002670035791465</v>
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>[[85, 4], [11, 4]]</t>
+          <t>[[86, 3], [12, 3]]</t>
         </is>
       </c>
     </row>

--- a/slide_classification/TCGA_Results/Caption_based_aggregation/H-Optimus-1/1-MSIH/Output/cross_valid_avg_eval_metrics.xlsx
+++ b/slide_classification/TCGA_Results/Caption_based_aggregation/H-Optimus-1/1-MSIH/Output/cross_valid_avg_eval_metrics.xlsx
@@ -610,19 +610,19 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.8932038834951457</v>
+        <v>0.9029126213592233</v>
       </c>
       <c r="C8" t="n">
         <v>0.8865979381443299</v>
       </c>
       <c r="D8" t="n">
-        <v>0.8303571428571429</v>
+        <v>0.8214285714285714</v>
       </c>
       <c r="E8" t="n">
-        <v>0.801980198019802</v>
+        <v>0.8316831683168316</v>
       </c>
       <c r="F8" t="n">
-        <v>0.8530347906291051</v>
+        <v>0.8606555748122391</v>
       </c>
     </row>
     <row r="9">
@@ -632,19 +632,19 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.8545454545454545</v>
+        <v>0.8878787878787879</v>
       </c>
       <c r="C9" t="n">
         <v>0.771978021978022</v>
       </c>
       <c r="D9" t="n">
-        <v>0.8184782608695653</v>
+        <v>0.8130434782608695</v>
       </c>
       <c r="E9" t="n">
-        <v>0.7434456928838951</v>
+        <v>0.7963483146067416</v>
       </c>
       <c r="F9" t="n">
-        <v>0.7971118575692342</v>
+        <v>0.8173121506811053</v>
       </c>
     </row>
     <row r="10">
@@ -654,19 +654,19 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.8106934001670844</v>
+        <v>0.8316993464052287</v>
       </c>
       <c r="C10" t="n">
         <v>0.7633621645597694</v>
       </c>
       <c r="D10" t="n">
-        <v>0.7588121953983906</v>
+        <v>0.7495527728085868</v>
       </c>
       <c r="E10" t="n">
-        <v>0.6619812583668006</v>
+        <v>0.7062446535500427</v>
       </c>
       <c r="F10" t="n">
-        <v>0.7487122546230112</v>
+        <v>0.762714734330907</v>
       </c>
     </row>
     <row r="11">
@@ -676,19 +676,19 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.8992708307986795</v>
+        <v>0.9092899295640586</v>
       </c>
       <c r="C11" t="n">
         <v>0.888358449195538</v>
       </c>
       <c r="D11" t="n">
-        <v>0.8432586907595407</v>
+        <v>0.8358037311525683</v>
       </c>
       <c r="E11" t="n">
-        <v>0.8278261561095868</v>
+        <v>0.8525895874446299</v>
       </c>
       <c r="F11" t="n">
-        <v>0.8646785317158363</v>
+        <v>0.8715104243391987</v>
       </c>
     </row>
     <row r="12">
@@ -698,19 +698,19 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.9265151515151514</v>
+        <v>0.9401515151515152</v>
       </c>
       <c r="C12" t="n">
         <v>0.8974358974358974</v>
       </c>
       <c r="D12" t="n">
-        <v>0.9391304347826087</v>
+        <v>0.9217391304347825</v>
       </c>
       <c r="E12" t="n">
-        <v>0.8923220973782772</v>
+        <v>0.8932584269662921</v>
       </c>
       <c r="F12" t="n">
-        <v>0.9138508952779836</v>
+        <v>0.9131462424971217</v>
       </c>
     </row>
     <row r="13">
@@ -721,7 +721,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>[[80, 8], [3, 12]]</t>
+          <t>[[80, 8], [2, 13]]</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -731,17 +731,17 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>[[77, 15], [4, 16]]</t>
+          <t>[[76, 16], [4, 16]]</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>[[73, 16], [4, 8]]</t>
+          <t>[[75, 14], [3, 9]]</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>[[77, 11], [4, 11]]</t>
+          <t>[[77, 11], [4, 12]]</t>
         </is>
       </c>
     </row>
@@ -1348,38 +1348,38 @@
         <v>413</v>
       </c>
       <c r="F3" t="n">
-        <v>0.8530347906291051</v>
+        <v>0.8606555748122391</v>
       </c>
       <c r="G3" t="n">
-        <v>0.03827821844006202</v>
+        <v>0.03477363344089026</v>
       </c>
       <c r="H3" t="n">
-        <v>0.7971118575692342</v>
+        <v>0.8173121506811053</v>
       </c>
       <c r="I3" t="n">
-        <v>0.04262308111569167</v>
+        <v>0.04327972243973256</v>
       </c>
       <c r="J3" t="n">
-        <v>0.7487122546230112</v>
+        <v>0.762714734330907</v>
       </c>
       <c r="K3" t="n">
-        <v>0.05403831228714425</v>
+        <v>0.04505941389836942</v>
       </c>
       <c r="L3" t="n">
-        <v>0.8646785317158363</v>
+        <v>0.8715104243391987</v>
       </c>
       <c r="M3" t="n">
-        <v>0.02989261121957837</v>
+        <v>0.02891415295192856</v>
       </c>
       <c r="N3" t="n">
-        <v>0.9138508952779836</v>
+        <v>0.9131462424971217</v>
       </c>
       <c r="O3" t="n">
-        <v>0.01957281147899201</v>
+        <v>0.01900962008285786</v>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>[[77, 11], [4, 11]]</t>
+          <t>[[77, 11], [4, 12]]</t>
         </is>
       </c>
     </row>
